--- a/02_Proteins/01_Design/c_data/01_design.xlsx
+++ b/02_Proteins/01_Design/c_data/01_design.xlsx
@@ -146,7 +146,7 @@
     <t>proteins</t>
   </si>
   <si>
-    <t>01_Preprocess/03_Quantification/c_data/proteins.rds</t>
+    <t>01_Preprocess/03_Quantify/c_data/proteins.rds</t>
   </si>
   <si>
     <t>34ef12f3ddbea70e6840925bab8692c5</t>
